--- a/financial_advisor_forms/005_financial_approval_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/005_financial_approval_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_1</t>
+          <t>financial_information_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Approval</t>
+          <t>Financial Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>budget_request_page_2</t>
+          <t>budget_request_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>expense_reimbursement_page_3</t>
+          <t>expense_reimbursement_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>funding_allocation_page_4</t>
+          <t>funding_allocation_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,35 +612,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_5</t>
+          <t>approval_status_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Approval</t>
+          <t>Approval Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>approval_status_6</t>
+          <t>notes_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Approval Status</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,23 +653,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notes_7</t>
+          <t>email_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email_8</t>
+          <t>phone_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>phone_9</t>
+          <t>financial_approval_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Financial Approval</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>financial_approval_form_10</t>
+          <t>date_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Financial Approval</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date_11</t>
+          <t>time_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,40 +768,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time_12</t>
+          <t>financial_approvals_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Financial Approvals</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>financial_approval_form_13</t>
+          <t>financial_notes_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Approval</t>
+          <t>Financial Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,269 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>financial_approval_form_14</t>
+          <t>financial_details_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Financial Approval</t>
+          <t>Financial Details</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>financial_approval_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>financial_approval_form_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>financial_approval_form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>financial_approval_form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>financial_approval_form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>financial_approval_form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>financial_approval_form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>financial_approval_form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>financial_approval_form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>financial_approval_form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>financial_approval_form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Financial Approval</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,187 +873,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_5_choices</t>
+          <t>approval_status_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_5_choices</t>
+          <t>approval_status_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_5_choices</t>
+          <t>approval_status_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>financial_approval_form_page_5_choices</t>
+          <t>approval_status_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>approval_status_6_choices</t>
+          <t>financial_approvals_12_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>status1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>approval_status_6_choices</t>
+          <t>financial_approvals_12_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>status2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>approval_status_6_choices</t>
+          <t>financial_approvals_12_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>status3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>status3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>financial_approval_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>financial_approval_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option6</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>financial_approval_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>financial_approval_form_13_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option8</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option8</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
